--- a/.pic/Labs/lab_13_periph/tab_01.xlsx
+++ b/.pic/Labs/lab_13_periph/tab_01.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\voult\Desktop\APS-reborn\.pic\Labs\lab_13_periph\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153AABF2-221A-4478-895F-0478F0C279F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4065" yWindow="1935" windowWidth="22260" windowHeight="18090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4068" yWindow="1932" windowWidth="22260" windowHeight="17496"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,20 +24,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
-  <si>
-    <t>Переключатели</t>
-  </si>
-  <si>
-    <t>Светодиоды</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
   <si>
     <t>PS/2</t>
   </si>
   <si>
-    <t>Семисегментники</t>
-  </si>
-  <si>
     <t>uart_rx</t>
   </si>
   <si>
@@ -53,66 +38,9 @@
     <t>0x04</t>
   </si>
   <si>
-    <t>(R) Выставленное на переключателях значение</t>
-  </si>
-  <si>
-    <t>(RW) Зажигаемое на светодиодах значение</t>
-  </si>
-  <si>
-    <t>(R) Значение нажатой клавиши</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX0</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX1</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX2</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX3</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX4</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX5</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX6</t>
-  </si>
-  <si>
-    <t>(RW) Значение на HEX7</t>
-  </si>
-  <si>
-    <t>(W) Сброс</t>
-  </si>
-  <si>
-    <t>(RW) Битовая маска включения/отключения отдельных индикаторов</t>
-  </si>
-  <si>
-    <t>(R) Принятые данные</t>
-  </si>
-  <si>
-    <t>(RW) Бодрейт</t>
-  </si>
-  <si>
-    <t>(RW) бит четности</t>
-  </si>
-  <si>
-    <t>(RW) Стоповый бит</t>
-  </si>
-  <si>
-    <t>(R) Непрочитанные данные</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
-    <t>(RW) Режим мигания</t>
-  </si>
-  <si>
     <t>0x01</t>
   </si>
   <si>
@@ -158,12 +86,6 @@
     <t>0x000024</t>
   </si>
   <si>
-    <t>Младшая часть адреса</t>
-  </si>
-  <si>
-    <t>Название периферийного устройства, старшая часть адреса для обращения к нему, режим доступа (R/W/RW) и функционал</t>
-  </si>
-  <si>
     <t>0x000028</t>
   </si>
   <si>
@@ -173,28 +95,97 @@
     <t>0xFFFFFC</t>
   </si>
   <si>
-    <t>(RW) Бит четности</t>
-  </si>
-  <si>
-    <t>(R) Сигнал busy</t>
-  </si>
-  <si>
-    <t>Видеоадаптер</t>
-  </si>
-  <si>
     <t>0x07</t>
   </si>
   <si>
-    <t>См. рис. 4</t>
-  </si>
-  <si>
-    <t>(RW) Отправляемые данные</t>
+    <t>Lower part of the address</t>
+  </si>
+  <si>
+    <t>Peripheral device name, upper part of the address used to access it, access mode (R/W/RW) and functionality</t>
+  </si>
+  <si>
+    <t>Switches</t>
+  </si>
+  <si>
+    <t>LEDs</t>
+  </si>
+  <si>
+    <t>Seven-segment displays</t>
+  </si>
+  <si>
+    <t>Video adapter</t>
+  </si>
+  <si>
+    <t>(R) Value set on the switches</t>
+  </si>
+  <si>
+    <t>(RW) Value lit on the LEDs</t>
+  </si>
+  <si>
+    <t>(R) Value of the pressed key</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX0</t>
+  </si>
+  <si>
+    <t>(R) Received data</t>
+  </si>
+  <si>
+    <t>(RW) Transmitted data</t>
+  </si>
+  <si>
+    <t>See fig. 4</t>
+  </si>
+  <si>
+    <t>(RW) Blink mode</t>
+  </si>
+  <si>
+    <t>(R) Unread data</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX1</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX2</t>
+  </si>
+  <si>
+    <t>(R) Busy signal</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX3</t>
+  </si>
+  <si>
+    <t>(RW) Baud rate</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX4</t>
+  </si>
+  <si>
+    <t>(RW) Parity bit</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX5</t>
+  </si>
+  <si>
+    <t>(RW) Stop bit</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX6</t>
+  </si>
+  <si>
+    <t>(RW) Value on HEX7</t>
+  </si>
+  <si>
+    <t>(RW) Bit mask for enabling/disabling individual displays</t>
+  </si>
+  <si>
+    <t>(W) Reset</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -403,27 +394,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,394 +727,394 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="F7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="16"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="22"/>
-      <c r="B2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="G7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="16"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="F11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="F12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="B14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="17"/>
-    </row>
-    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="B16" s="9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -1177,7 +1168,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1"/>
@@ -1186,34 +1177,34 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
